--- a/data/teams/leagues/Averages_Sweden_Allsvenskan_2025.xlsx
+++ b/data/teams/leagues/Averages_Sweden_Allsvenskan_2025.xlsx
@@ -137,7 +137,7 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="AveragesTable" displayName="AveragesTable" ref="A1:EC17" headerRowCount="1">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="AveragesTable_Sweden_All" displayName="AveragesTable_Sweden_All" ref="A1:EC17" headerRowCount="1">
   <autoFilter ref="A1:EC17"/>
   <tableColumns count="133">
     <tableColumn id="1" name="team_name"/>
@@ -1613,13 +1613,13 @@
         <v>3.38</v>
       </c>
       <c r="CB2" t="n">
-        <v>3.52</v>
+        <v>3.51</v>
       </c>
       <c r="CC2" t="n">
         <v>2.78</v>
       </c>
       <c r="CD2" t="n">
-        <v>3.03</v>
+        <v>2.91</v>
       </c>
       <c r="CE2" t="n">
         <v>1.44</v>
@@ -1664,13 +1664,13 @@
         <v>1.47</v>
       </c>
       <c r="CS2" t="n">
-        <v>3.15</v>
+        <v>3.17</v>
       </c>
       <c r="CT2" t="n">
-        <v>2.8</v>
+        <v>2.79</v>
       </c>
       <c r="CU2" t="n">
-        <v>1.38</v>
+        <v>1.37</v>
       </c>
       <c r="CV2" t="n">
         <v>1.88</v>
@@ -1688,7 +1688,7 @@
         <v>2.51</v>
       </c>
       <c r="DA2" t="n">
-        <v>2.15</v>
+        <v>2.16</v>
       </c>
       <c r="DB2" t="n">
         <v>1.39</v>
@@ -1697,7 +1697,7 @@
         <v>2.23</v>
       </c>
       <c r="DD2" t="n">
-        <v>4.08</v>
+        <v>4.09</v>
       </c>
       <c r="DE2" t="n">
         <v>0.04</v>
@@ -2010,19 +2010,19 @@
         <v>2.56</v>
       </c>
       <c r="BZ3" t="n">
-        <v>2.66</v>
+        <v>2.69</v>
       </c>
       <c r="CA3" t="n">
         <v>3.7</v>
       </c>
       <c r="CB3" t="n">
-        <v>3.96</v>
+        <v>3.93</v>
       </c>
       <c r="CC3" t="n">
         <v>3.72</v>
       </c>
       <c r="CD3" t="n">
-        <v>4.1</v>
+        <v>3.99</v>
       </c>
       <c r="CE3" t="n">
         <v>1.29</v>
@@ -2064,22 +2064,22 @@
         <v>2.57</v>
       </c>
       <c r="CR3" t="n">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="CS3" t="n">
-        <v>2.49</v>
+        <v>2.51</v>
       </c>
       <c r="CT3" t="n">
-        <v>3.25</v>
+        <v>3.23</v>
       </c>
       <c r="CU3" t="n">
         <v>1.56</v>
       </c>
       <c r="CV3" t="n">
-        <v>2.38</v>
+        <v>2.36</v>
       </c>
       <c r="CW3" t="n">
-        <v>1.62</v>
+        <v>1.63</v>
       </c>
       <c r="CX3" t="n">
         <v>1.47</v>
@@ -2094,13 +2094,13 @@
         <v>2.41</v>
       </c>
       <c r="DB3" t="n">
-        <v>1.2</v>
+        <v>1.21</v>
       </c>
       <c r="DC3" t="n">
-        <v>1.67</v>
+        <v>1.69</v>
       </c>
       <c r="DD3" t="n">
-        <v>2.64</v>
+        <v>2.69</v>
       </c>
       <c r="DE3" t="n">
         <v>0.06</v>
@@ -2425,7 +2425,7 @@
         <v>4.64</v>
       </c>
       <c r="CD4" t="n">
-        <v>4.95</v>
+        <v>4.79</v>
       </c>
       <c r="CE4" t="n">
         <v>1.36</v>
@@ -2470,19 +2470,19 @@
         <v>1.4</v>
       </c>
       <c r="CS4" t="n">
-        <v>2.85</v>
+        <v>2.83</v>
       </c>
       <c r="CT4" t="n">
-        <v>3.03</v>
+        <v>3.06</v>
       </c>
       <c r="CU4" t="n">
         <v>1.45</v>
       </c>
       <c r="CV4" t="n">
-        <v>2.1</v>
+        <v>2.12</v>
       </c>
       <c r="CW4" t="n">
-        <v>1.79</v>
+        <v>1.78</v>
       </c>
       <c r="CX4" t="n">
         <v>1.45</v>
@@ -2494,16 +2494,16 @@
         <v>2.59</v>
       </c>
       <c r="DA4" t="n">
-        <v>2.36</v>
+        <v>2.35</v>
       </c>
       <c r="DB4" t="n">
         <v>1.28</v>
       </c>
       <c r="DC4" t="n">
-        <v>1.9</v>
+        <v>1.89</v>
       </c>
       <c r="DD4" t="n">
-        <v>3.22</v>
+        <v>3.19</v>
       </c>
       <c r="DE4" t="n">
         <v>0.1</v>
@@ -2816,19 +2816,19 @@
         <v>1.88</v>
       </c>
       <c r="BZ5" t="n">
-        <v>2</v>
+        <v>1.98</v>
       </c>
       <c r="CA5" t="n">
         <v>3.72</v>
       </c>
       <c r="CB5" t="n">
-        <v>3.96</v>
+        <v>3.94</v>
       </c>
       <c r="CC5" t="n">
         <v>2.61</v>
       </c>
       <c r="CD5" t="n">
-        <v>2.63</v>
+        <v>2.68</v>
       </c>
       <c r="CE5" t="n">
         <v>1.34</v>
@@ -2873,13 +2873,13 @@
         <v>1.4</v>
       </c>
       <c r="CS5" t="n">
-        <v>2.69</v>
+        <v>2.71</v>
       </c>
       <c r="CT5" t="n">
-        <v>3.05</v>
+        <v>3.06</v>
       </c>
       <c r="CU5" t="n">
-        <v>1.51</v>
+        <v>1.5</v>
       </c>
       <c r="CV5" t="n">
         <v>2.18</v>
@@ -2888,13 +2888,13 @@
         <v>1.74</v>
       </c>
       <c r="CX5" t="n">
-        <v>1.53</v>
+        <v>1.52</v>
       </c>
       <c r="CY5" t="n">
         <v>1.67</v>
       </c>
       <c r="CZ5" t="n">
-        <v>2.45</v>
+        <v>2.47</v>
       </c>
       <c r="DA5" t="n">
         <v>2.19</v>
@@ -2906,7 +2906,7 @@
         <v>1.84</v>
       </c>
       <c r="DD5" t="n">
-        <v>3.07</v>
+        <v>3.09</v>
       </c>
       <c r="DE5" t="n">
         <v>0.16</v>
@@ -3219,13 +3219,13 @@
         <v>2.05</v>
       </c>
       <c r="BZ6" t="n">
-        <v>2.13</v>
+        <v>2.1</v>
       </c>
       <c r="CA6" t="n">
         <v>3.67</v>
       </c>
       <c r="CB6" t="n">
-        <v>3.85</v>
+        <v>3.87</v>
       </c>
       <c r="CC6" t="n">
         <v>3.2</v>
@@ -3306,10 +3306,10 @@
         <v>1.24</v>
       </c>
       <c r="DC6" t="n">
-        <v>1.77</v>
+        <v>1.76</v>
       </c>
       <c r="DD6" t="n">
-        <v>2.9</v>
+        <v>2.88</v>
       </c>
       <c r="DE6" t="n">
         <v>0.1</v>
@@ -4025,19 +4025,19 @@
         <v>3.72</v>
       </c>
       <c r="BZ8" t="n">
-        <v>3.88</v>
+        <v>3.85</v>
       </c>
       <c r="CA8" t="n">
         <v>3.85</v>
       </c>
       <c r="CB8" t="n">
-        <v>4.13</v>
+        <v>4.1</v>
       </c>
       <c r="CC8" t="n">
         <v>6.58</v>
       </c>
       <c r="CD8" t="n">
-        <v>7.23</v>
+        <v>6.95</v>
       </c>
       <c r="CE8" t="n">
         <v>1.36</v>
@@ -4082,13 +4082,13 @@
         <v>1.4</v>
       </c>
       <c r="CS8" t="n">
-        <v>2.86</v>
+        <v>2.88</v>
       </c>
       <c r="CT8" t="n">
-        <v>3.08</v>
+        <v>3.07</v>
       </c>
       <c r="CU8" t="n">
-        <v>1.45</v>
+        <v>1.44</v>
       </c>
       <c r="CV8" t="n">
         <v>1.97</v>
@@ -4100,22 +4100,22 @@
         <v>1.52</v>
       </c>
       <c r="CY8" t="n">
-        <v>1.68</v>
+        <v>1.67</v>
       </c>
       <c r="CZ8" t="n">
         <v>2.49</v>
       </c>
       <c r="DA8" t="n">
-        <v>2.17</v>
+        <v>2.18</v>
       </c>
       <c r="DB8" t="n">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="DC8" t="n">
-        <v>1.91</v>
+        <v>1.93</v>
       </c>
       <c r="DD8" t="n">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="DE8" t="n">
         <v>0</v>
@@ -4428,19 +4428,19 @@
         <v>1.64</v>
       </c>
       <c r="BZ9" t="n">
-        <v>1.64</v>
+        <v>1.69</v>
       </c>
       <c r="CA9" t="n">
         <v>3.91</v>
       </c>
       <c r="CB9" t="n">
-        <v>4.14</v>
+        <v>4.08</v>
       </c>
       <c r="CC9" t="n">
         <v>2.2</v>
       </c>
       <c r="CD9" t="n">
-        <v>2.26</v>
+        <v>2.27</v>
       </c>
       <c r="CE9" t="n">
         <v>1.31</v>
@@ -4482,39 +4482,43 @@
         <v>2.8</v>
       </c>
       <c r="CR9" t="n">
-        <v>1.38</v>
+        <v>1.39</v>
       </c>
       <c r="CS9" t="n">
-        <v>2.57</v>
+        <v>2.61</v>
       </c>
       <c r="CT9" t="n">
-        <v>3.13</v>
+        <v>3.11</v>
       </c>
       <c r="CU9" t="n">
-        <v>1.54</v>
+        <v>1.53</v>
       </c>
       <c r="CV9" t="n">
-        <v>2.25</v>
+        <v>2.24</v>
       </c>
       <c r="CW9" t="n">
-        <v>1.69</v>
-      </c>
-      <c r="CX9" t="inlineStr"/>
+        <v>1.7</v>
+      </c>
+      <c r="CX9" t="n">
+        <v>1.44</v>
+      </c>
       <c r="CY9" t="n">
-        <v>1.58</v>
-      </c>
-      <c r="CZ9" t="inlineStr"/>
+        <v>1.6</v>
+      </c>
+      <c r="CZ9" t="n">
+        <v>2.64</v>
+      </c>
       <c r="DA9" t="n">
-        <v>2.31</v>
+        <v>2.28</v>
       </c>
       <c r="DB9" t="n">
         <v>1.23</v>
       </c>
       <c r="DC9" t="n">
-        <v>1.74</v>
+        <v>1.76</v>
       </c>
       <c r="DD9" t="n">
-        <v>2.83</v>
+        <v>2.88</v>
       </c>
       <c r="DE9" t="n">
         <v>0.1</v>
@@ -4833,13 +4837,13 @@
         <v>3.69</v>
       </c>
       <c r="CB10" t="n">
-        <v>3.88</v>
+        <v>3.89</v>
       </c>
       <c r="CC10" t="n">
         <v>3.09</v>
       </c>
       <c r="CD10" t="n">
-        <v>3.28</v>
+        <v>3.29</v>
       </c>
       <c r="CE10" t="n">
         <v>1.29</v>
@@ -4887,13 +4891,13 @@
         <v>2.53</v>
       </c>
       <c r="CT10" t="n">
-        <v>3.21</v>
+        <v>3.22</v>
       </c>
       <c r="CU10" t="n">
         <v>1.56</v>
       </c>
       <c r="CV10" t="n">
-        <v>2.43</v>
+        <v>2.44</v>
       </c>
       <c r="CW10" t="n">
         <v>1.6</v>
@@ -4902,22 +4906,22 @@
         <v>1.46</v>
       </c>
       <c r="CY10" t="n">
-        <v>1.55</v>
+        <v>1.54</v>
       </c>
       <c r="CZ10" t="n">
         <v>2.59</v>
       </c>
       <c r="DA10" t="n">
-        <v>2.38</v>
+        <v>2.39</v>
       </c>
       <c r="DB10" t="n">
         <v>1.21</v>
       </c>
       <c r="DC10" t="n">
-        <v>1.69</v>
+        <v>1.68</v>
       </c>
       <c r="DD10" t="n">
-        <v>2.67</v>
+        <v>2.66</v>
       </c>
       <c r="DE10" t="n">
         <v>0.06</v>
@@ -5230,13 +5234,13 @@
         <v>2.11</v>
       </c>
       <c r="BZ11" t="n">
-        <v>2.17</v>
+        <v>2.13</v>
       </c>
       <c r="CA11" t="n">
         <v>3.59</v>
       </c>
       <c r="CB11" t="n">
-        <v>3.75</v>
+        <v>3.77</v>
       </c>
       <c r="CC11" t="n">
         <v>3.03</v>
@@ -5287,19 +5291,19 @@
         <v>1.39</v>
       </c>
       <c r="CS11" t="n">
-        <v>2.69</v>
+        <v>2.7</v>
       </c>
       <c r="CT11" t="n">
-        <v>3.12</v>
+        <v>3.11</v>
       </c>
       <c r="CU11" t="n">
-        <v>1.51</v>
+        <v>1.5</v>
       </c>
       <c r="CV11" t="n">
-        <v>2.25</v>
+        <v>2.23</v>
       </c>
       <c r="CW11" t="n">
-        <v>1.69</v>
+        <v>1.7</v>
       </c>
       <c r="CX11" t="inlineStr"/>
       <c r="CY11" t="n">
@@ -5307,7 +5311,7 @@
       </c>
       <c r="CZ11" t="inlineStr"/>
       <c r="DA11" t="n">
-        <v>2.38</v>
+        <v>2.37</v>
       </c>
       <c r="DB11" t="n">
         <v>1.25</v>
@@ -5316,7 +5320,7 @@
         <v>1.82</v>
       </c>
       <c r="DD11" t="n">
-        <v>3.01</v>
+        <v>3.03</v>
       </c>
       <c r="DE11" t="n">
         <v>0.1</v>
@@ -5629,19 +5633,19 @@
         <v>1.58</v>
       </c>
       <c r="BZ12" t="n">
-        <v>1.55</v>
+        <v>1.6</v>
       </c>
       <c r="CA12" t="n">
         <v>3.87</v>
       </c>
       <c r="CB12" t="n">
-        <v>4.3</v>
+        <v>4.26</v>
       </c>
       <c r="CC12" t="n">
         <v>2.09</v>
       </c>
       <c r="CD12" t="n">
-        <v>2.21</v>
+        <v>2.25</v>
       </c>
       <c r="CE12" t="n">
         <v>1.32</v>
@@ -5686,7 +5690,7 @@
         <v>1.39</v>
       </c>
       <c r="CS12" t="n">
-        <v>2.7</v>
+        <v>2.69</v>
       </c>
       <c r="CT12" t="n">
         <v>3.11</v>
@@ -5695,27 +5699,31 @@
         <v>1.5</v>
       </c>
       <c r="CV12" t="n">
-        <v>2.04</v>
+        <v>2.08</v>
       </c>
       <c r="CW12" t="n">
-        <v>1.84</v>
-      </c>
-      <c r="CX12" t="inlineStr"/>
+        <v>1.81</v>
+      </c>
+      <c r="CX12" t="n">
+        <v>1.44</v>
+      </c>
       <c r="CY12" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="CZ12" t="inlineStr"/>
+        <v>1.58</v>
+      </c>
+      <c r="CZ12" t="n">
+        <v>2.67</v>
+      </c>
       <c r="DA12" t="n">
-        <v>2.34</v>
+        <v>2.32</v>
       </c>
       <c r="DB12" t="n">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="DC12" t="n">
-        <v>1.82</v>
+        <v>1.81</v>
       </c>
       <c r="DD12" t="n">
-        <v>3.02</v>
+        <v>3</v>
       </c>
       <c r="DE12" t="n">
         <v>0.17</v>
@@ -6028,13 +6036,13 @@
         <v>1.85</v>
       </c>
       <c r="BZ13" t="n">
-        <v>1.88</v>
+        <v>1.85</v>
       </c>
       <c r="CA13" t="n">
         <v>3.62</v>
       </c>
       <c r="CB13" t="n">
-        <v>3.8</v>
+        <v>3.84</v>
       </c>
       <c r="CC13" t="n">
         <v>2.61</v>
@@ -6085,16 +6093,16 @@
         <v>1.4</v>
       </c>
       <c r="CS13" t="n">
-        <v>2.8</v>
+        <v>2.78</v>
       </c>
       <c r="CT13" t="n">
-        <v>3.06</v>
+        <v>3.07</v>
       </c>
       <c r="CU13" t="n">
         <v>1.47</v>
       </c>
       <c r="CV13" t="n">
-        <v>2.09</v>
+        <v>2.08</v>
       </c>
       <c r="CW13" t="n">
         <v>1.81</v>
@@ -6115,10 +6123,10 @@
         <v>1.28</v>
       </c>
       <c r="DC13" t="n">
-        <v>1.91</v>
+        <v>1.9</v>
       </c>
       <c r="DD13" t="n">
-        <v>3.26</v>
+        <v>3.23</v>
       </c>
       <c r="DE13" t="n">
         <v>0.13</v>
@@ -6431,13 +6439,13 @@
         <v>2.98</v>
       </c>
       <c r="BZ14" t="n">
-        <v>3.03</v>
+        <v>3.15</v>
       </c>
       <c r="CA14" t="n">
         <v>3.85</v>
       </c>
       <c r="CB14" t="n">
-        <v>3.99</v>
+        <v>4.02</v>
       </c>
       <c r="CC14" t="n">
         <v>4.72</v>
@@ -6488,7 +6496,7 @@
         <v>1.36</v>
       </c>
       <c r="CS14" t="n">
-        <v>2.52</v>
+        <v>2.51</v>
       </c>
       <c r="CT14" t="n">
         <v>3.2</v>
@@ -6497,10 +6505,10 @@
         <v>1.56</v>
       </c>
       <c r="CV14" t="n">
-        <v>2.34</v>
+        <v>2.36</v>
       </c>
       <c r="CW14" t="n">
-        <v>1.65</v>
+        <v>1.64</v>
       </c>
       <c r="CX14" t="inlineStr"/>
       <c r="CY14" t="n">
@@ -6511,13 +6519,13 @@
         <v>2.46</v>
       </c>
       <c r="DB14" t="n">
-        <v>1.22</v>
+        <v>1.21</v>
       </c>
       <c r="DC14" t="n">
-        <v>1.71</v>
+        <v>1.7</v>
       </c>
       <c r="DD14" t="n">
-        <v>2.75</v>
+        <v>2.72</v>
       </c>
       <c r="DE14" t="n">
         <v>0.13</v>
@@ -6830,19 +6838,19 @@
         <v>2.47</v>
       </c>
       <c r="BZ15" t="n">
-        <v>2.37</v>
+        <v>2.46</v>
       </c>
       <c r="CA15" t="n">
         <v>3.7</v>
       </c>
       <c r="CB15" t="n">
-        <v>4.01</v>
+        <v>3.99</v>
       </c>
       <c r="CC15" t="n">
         <v>3.75</v>
       </c>
       <c r="CD15" t="n">
-        <v>4.05</v>
+        <v>3.93</v>
       </c>
       <c r="CE15" t="n">
         <v>1.3</v>
@@ -6884,28 +6892,28 @@
         <v>2.68</v>
       </c>
       <c r="CR15" t="n">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="CS15" t="n">
-        <v>2.51</v>
+        <v>2.55</v>
       </c>
       <c r="CT15" t="n">
-        <v>3.2</v>
+        <v>3.16</v>
       </c>
       <c r="CU15" t="n">
-        <v>1.57</v>
+        <v>1.56</v>
       </c>
       <c r="CV15" t="n">
         <v>2.37</v>
       </c>
       <c r="CW15" t="n">
-        <v>1.63</v>
+        <v>1.64</v>
       </c>
       <c r="CX15" t="n">
         <v>1.47</v>
       </c>
       <c r="CY15" t="n">
-        <v>1.54</v>
+        <v>1.55</v>
       </c>
       <c r="CZ15" t="n">
         <v>2.56</v>
@@ -6917,10 +6925,10 @@
         <v>1.21</v>
       </c>
       <c r="DC15" t="n">
-        <v>1.68</v>
+        <v>1.7</v>
       </c>
       <c r="DD15" t="n">
-        <v>2.68</v>
+        <v>2.71</v>
       </c>
       <c r="DE15" t="n">
         <v>0.2</v>
@@ -7233,19 +7241,19 @@
         <v>3.45</v>
       </c>
       <c r="BZ16" t="n">
-        <v>3.64</v>
+        <v>3.47</v>
       </c>
       <c r="CA16" t="n">
         <v>3.93</v>
       </c>
       <c r="CB16" t="n">
-        <v>4.37</v>
+        <v>4.28</v>
       </c>
       <c r="CC16" t="n">
         <v>5.54</v>
       </c>
       <c r="CD16" t="n">
-        <v>6.45</v>
+        <v>6.11</v>
       </c>
       <c r="CE16" t="n">
         <v>1.32</v>
@@ -7287,22 +7295,22 @@
         <v>2.85</v>
       </c>
       <c r="CR16" t="n">
-        <v>1.4</v>
+        <v>1.39</v>
       </c>
       <c r="CS16" t="n">
-        <v>2.46</v>
+        <v>2.51</v>
       </c>
       <c r="CT16" t="n">
-        <v>3.08</v>
+        <v>3.11</v>
       </c>
       <c r="CU16" t="n">
-        <v>1.61</v>
+        <v>1.59</v>
       </c>
       <c r="CV16" t="n">
-        <v>2.22</v>
+        <v>2.21</v>
       </c>
       <c r="CW16" t="n">
-        <v>1.72</v>
+        <v>1.73</v>
       </c>
       <c r="CX16" t="inlineStr"/>
       <c r="CY16" t="n">
@@ -7310,16 +7318,16 @@
       </c>
       <c r="CZ16" t="inlineStr"/>
       <c r="DA16" t="n">
-        <v>2.4</v>
+        <v>2.38</v>
       </c>
       <c r="DB16" t="n">
-        <v>1.23</v>
+        <v>1.24</v>
       </c>
       <c r="DC16" t="n">
-        <v>1.74</v>
+        <v>1.76</v>
       </c>
       <c r="DD16" t="n">
-        <v>2.86</v>
+        <v>2.9</v>
       </c>
       <c r="DE16" t="n">
         <v>0.1</v>
@@ -7632,13 +7640,13 @@
         <v>3.51</v>
       </c>
       <c r="BZ17" t="n">
-        <v>3.74</v>
+        <v>3.68</v>
       </c>
       <c r="CA17" t="n">
         <v>3.63</v>
       </c>
       <c r="CB17" t="n">
-        <v>4.12</v>
+        <v>4.07</v>
       </c>
       <c r="CC17" t="n">
         <v>4.85</v>
@@ -7686,39 +7694,39 @@
         <v>2.9</v>
       </c>
       <c r="CR17" t="n">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="CS17" t="n">
-        <v>2.68</v>
+        <v>2.7</v>
       </c>
       <c r="CT17" t="n">
-        <v>3.18</v>
+        <v>3.16</v>
       </c>
       <c r="CU17" t="n">
         <v>1.49</v>
       </c>
       <c r="CV17" t="n">
-        <v>2.07</v>
+        <v>2.08</v>
       </c>
       <c r="CW17" t="n">
         <v>1.81</v>
       </c>
       <c r="CX17" t="inlineStr"/>
       <c r="CY17" t="n">
-        <v>1.5</v>
+        <v>1.51</v>
       </c>
       <c r="CZ17" t="inlineStr"/>
       <c r="DA17" t="n">
-        <v>2.48</v>
+        <v>2.47</v>
       </c>
       <c r="DB17" t="n">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="DC17" t="n">
-        <v>1.8</v>
+        <v>1.82</v>
       </c>
       <c r="DD17" t="n">
-        <v>2.98</v>
+        <v>3.02</v>
       </c>
       <c r="DE17" t="n">
         <v>0.1</v>

--- a/data/teams/leagues/Averages_Sweden_Allsvenskan_2025.xlsx
+++ b/data/teams/leagues/Averages_Sweden_Allsvenskan_2025.xlsx
@@ -1532,10 +1532,10 @@
         <v>0.13</v>
       </c>
       <c r="BA2" t="n">
-        <v>11.27</v>
+        <v>11.13</v>
       </c>
       <c r="BB2" t="n">
-        <v>8.27</v>
+        <v>8.130000000000001</v>
       </c>
       <c r="BC2" t="n">
         <v>3</v>
@@ -1544,7 +1544,7 @@
         <v>24.93</v>
       </c>
       <c r="BE2" t="n">
-        <v>1.27</v>
+        <v>1.26</v>
       </c>
       <c r="BF2" t="n">
         <v>2.27</v>
@@ -1757,10 +1757,10 @@
         <v>0.06</v>
       </c>
       <c r="DX2" t="n">
-        <v>12.93</v>
+        <v>12.87</v>
       </c>
       <c r="DY2" t="n">
-        <v>9.300000000000001</v>
+        <v>9.23</v>
       </c>
       <c r="DZ2" t="n">
         <v>3.64</v>
@@ -1769,7 +1769,7 @@
         <v>25.23</v>
       </c>
       <c r="EB2" t="n">
-        <v>1.41</v>
+        <v>1.4</v>
       </c>
       <c r="EC2" t="n">
         <v>2.13</v>
@@ -1854,10 +1854,10 @@
         <v>0</v>
       </c>
       <c r="Z3" t="n">
-        <v>12.6</v>
+        <v>12.67</v>
       </c>
       <c r="AA3" t="n">
-        <v>8</v>
+        <v>8.07</v>
       </c>
       <c r="AB3" t="n">
         <v>4.6</v>
@@ -1929,16 +1929,16 @@
         <v>0</v>
       </c>
       <c r="AY3" t="n">
-        <v>39.47</v>
+        <v>39.53</v>
       </c>
       <c r="AZ3" t="n">
         <v>0</v>
       </c>
       <c r="BA3" t="n">
-        <v>12.87</v>
+        <v>12.93</v>
       </c>
       <c r="BB3" t="n">
-        <v>8.529999999999999</v>
+        <v>8.6</v>
       </c>
       <c r="BC3" t="n">
         <v>4.33</v>
@@ -1947,7 +1947,7 @@
         <v>19.07</v>
       </c>
       <c r="BE3" t="n">
-        <v>1.41</v>
+        <v>1.42</v>
       </c>
       <c r="BF3" t="n">
         <v>1.87</v>
@@ -2154,16 +2154,16 @@
         <v>0</v>
       </c>
       <c r="DV3" t="n">
-        <v>43.37</v>
+        <v>43.4</v>
       </c>
       <c r="DW3" t="n">
         <v>0</v>
       </c>
       <c r="DX3" t="n">
-        <v>12.73</v>
+        <v>12.8</v>
       </c>
       <c r="DY3" t="n">
-        <v>8.26</v>
+        <v>8.34</v>
       </c>
       <c r="DZ3" t="n">
         <v>4.46</v>
@@ -2332,7 +2332,7 @@
         <v>0</v>
       </c>
       <c r="AY4" t="n">
-        <v>38.87</v>
+        <v>38.8</v>
       </c>
       <c r="AZ4" t="n">
         <v>0.13</v>
@@ -2341,16 +2341,16 @@
         <v>12.27</v>
       </c>
       <c r="BB4" t="n">
-        <v>7.73</v>
+        <v>7.87</v>
       </c>
       <c r="BC4" t="n">
-        <v>4.53</v>
+        <v>4.4</v>
       </c>
       <c r="BD4" t="n">
         <v>18.33</v>
       </c>
       <c r="BE4" t="n">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="BF4" t="n">
         <v>2.33</v>
@@ -2557,7 +2557,7 @@
         <v>0</v>
       </c>
       <c r="DV4" t="n">
-        <v>43.67</v>
+        <v>43.64</v>
       </c>
       <c r="DW4" t="n">
         <v>0.06</v>
@@ -2566,16 +2566,16 @@
         <v>12.67</v>
       </c>
       <c r="DY4" t="n">
-        <v>8.76</v>
+        <v>8.84</v>
       </c>
       <c r="DZ4" t="n">
-        <v>3.9</v>
+        <v>3.84</v>
       </c>
       <c r="EA4" t="n">
         <v>21.83</v>
       </c>
       <c r="EB4" t="n">
-        <v>1.41</v>
+        <v>1.4</v>
       </c>
       <c r="EC4" t="n">
         <v>2.13</v>
@@ -3063,10 +3063,10 @@
         <v>0</v>
       </c>
       <c r="Z6" t="n">
-        <v>13.53</v>
+        <v>13.47</v>
       </c>
       <c r="AA6" t="n">
-        <v>8.800000000000001</v>
+        <v>8.73</v>
       </c>
       <c r="AB6" t="n">
         <v>4.73</v>
@@ -3120,7 +3120,7 @@
         <v>12.13</v>
       </c>
       <c r="AS6" t="n">
-        <v>9.07</v>
+        <v>9</v>
       </c>
       <c r="AT6" t="n">
         <v>1.6</v>
@@ -3138,7 +3138,7 @@
         <v>0</v>
       </c>
       <c r="AY6" t="n">
-        <v>48.67</v>
+        <v>48.73</v>
       </c>
       <c r="AZ6" t="n">
         <v>0.07000000000000001</v>
@@ -3351,7 +3351,7 @@
         <v>11.8</v>
       </c>
       <c r="DR6" t="n">
-        <v>8.44</v>
+        <v>8.4</v>
       </c>
       <c r="DS6" t="n">
         <v>0.06</v>
@@ -3363,16 +3363,16 @@
         <v>0</v>
       </c>
       <c r="DV6" t="n">
-        <v>48.84</v>
+        <v>48.86</v>
       </c>
       <c r="DW6" t="n">
         <v>0.04</v>
       </c>
       <c r="DX6" t="n">
-        <v>12.9</v>
+        <v>12.87</v>
       </c>
       <c r="DY6" t="n">
-        <v>8.56</v>
+        <v>8.529999999999999</v>
       </c>
       <c r="DZ6" t="n">
         <v>4.33</v>
@@ -3469,16 +3469,16 @@
         <v>19.13</v>
       </c>
       <c r="AA7" t="n">
-        <v>14</v>
+        <v>13.87</v>
       </c>
       <c r="AB7" t="n">
-        <v>5.13</v>
+        <v>5.27</v>
       </c>
       <c r="AC7" t="n">
         <v>24.27</v>
       </c>
       <c r="AD7" t="n">
-        <v>2.03</v>
+        <v>2.04</v>
       </c>
       <c r="AE7" t="n">
         <v>1.93</v>
@@ -3775,10 +3775,10 @@
         <v>16.23</v>
       </c>
       <c r="DY7" t="n">
-        <v>11.63</v>
+        <v>11.57</v>
       </c>
       <c r="DZ7" t="n">
-        <v>4.6</v>
+        <v>4.67</v>
       </c>
       <c r="EA7" t="n">
         <v>23.14</v>
@@ -3863,16 +3863,16 @@
         <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>44.4</v>
+        <v>44.33</v>
       </c>
       <c r="Y8" t="n">
         <v>0.07000000000000001</v>
       </c>
       <c r="Z8" t="n">
-        <v>10.8</v>
+        <v>10.87</v>
       </c>
       <c r="AA8" t="n">
-        <v>7.73</v>
+        <v>7.8</v>
       </c>
       <c r="AB8" t="n">
         <v>3.07</v>
@@ -3881,7 +3881,7 @@
         <v>20.4</v>
       </c>
       <c r="AD8" t="n">
-        <v>1.16</v>
+        <v>1.17</v>
       </c>
       <c r="AE8" t="n">
         <v>1.93</v>
@@ -4169,16 +4169,16 @@
         <v>0</v>
       </c>
       <c r="DV8" t="n">
-        <v>40.24</v>
+        <v>40.2</v>
       </c>
       <c r="DW8" t="n">
         <v>0.07000000000000001</v>
       </c>
       <c r="DX8" t="n">
-        <v>10.14</v>
+        <v>10.17</v>
       </c>
       <c r="DY8" t="n">
-        <v>6.9</v>
+        <v>6.94</v>
       </c>
       <c r="DZ8" t="n">
         <v>3.24</v>
@@ -4732,7 +4732,7 @@
         <v>13.6</v>
       </c>
       <c r="AS10" t="n">
-        <v>9.130000000000001</v>
+        <v>9.07</v>
       </c>
       <c r="AT10" t="n">
         <v>1.4</v>
@@ -4756,10 +4756,10 @@
         <v>0</v>
       </c>
       <c r="BA10" t="n">
-        <v>14.93</v>
+        <v>15</v>
       </c>
       <c r="BB10" t="n">
-        <v>9.529999999999999</v>
+        <v>9.6</v>
       </c>
       <c r="BC10" t="n">
         <v>5.4</v>
@@ -4768,7 +4768,7 @@
         <v>19.8</v>
       </c>
       <c r="BE10" t="n">
-        <v>1.66</v>
+        <v>1.67</v>
       </c>
       <c r="BF10" t="n">
         <v>2.27</v>
@@ -4963,7 +4963,7 @@
         <v>12.76</v>
       </c>
       <c r="DR10" t="n">
-        <v>7.93</v>
+        <v>7.9</v>
       </c>
       <c r="DS10" t="n">
         <v>0.1</v>
@@ -4981,10 +4981,10 @@
         <v>0.1</v>
       </c>
       <c r="DX10" t="n">
-        <v>15.4</v>
+        <v>15.43</v>
       </c>
       <c r="DY10" t="n">
-        <v>9.93</v>
+        <v>9.960000000000001</v>
       </c>
       <c r="DZ10" t="n">
         <v>5.46</v>
@@ -5501,7 +5501,7 @@
         <v>1</v>
       </c>
       <c r="AH12" t="n">
-        <v>3.33</v>
+        <v>3.53</v>
       </c>
       <c r="AI12" t="n">
         <v>105.73</v>
@@ -5516,7 +5516,7 @@
         <v>5.73</v>
       </c>
       <c r="AM12" t="n">
-        <v>0.2</v>
+        <v>0.33</v>
       </c>
       <c r="AN12" t="n">
         <v>49.27</v>
@@ -5525,7 +5525,7 @@
         <v>0.6</v>
       </c>
       <c r="AP12" t="n">
-        <v>2.07</v>
+        <v>2.2</v>
       </c>
       <c r="AQ12" t="n">
         <v>10.93</v>
@@ -5552,16 +5552,16 @@
         <v>0</v>
       </c>
       <c r="AY12" t="n">
-        <v>56.67</v>
+        <v>56.6</v>
       </c>
       <c r="AZ12" t="n">
         <v>0.07000000000000001</v>
       </c>
       <c r="BA12" t="n">
-        <v>12.8</v>
+        <v>12.73</v>
       </c>
       <c r="BB12" t="n">
-        <v>8.4</v>
+        <v>8.33</v>
       </c>
       <c r="BC12" t="n">
         <v>4.4</v>
@@ -5570,7 +5570,7 @@
         <v>20.8</v>
       </c>
       <c r="BE12" t="n">
-        <v>1.48</v>
+        <v>1.47</v>
       </c>
       <c r="BF12" t="n">
         <v>1.53</v>
@@ -5603,10 +5603,10 @@
         <v>1.17</v>
       </c>
       <c r="BP12" t="n">
-        <v>4.5</v>
+        <v>4.67</v>
       </c>
       <c r="BQ12" t="n">
-        <v>5.57</v>
+        <v>5.77</v>
       </c>
       <c r="BR12" t="n">
         <v>86.67</v>
@@ -5732,7 +5732,7 @@
         <v>1.1</v>
       </c>
       <c r="DG12" t="n">
-        <v>3.56</v>
+        <v>3.66</v>
       </c>
       <c r="DH12" t="n">
         <v>108.73</v>
@@ -5747,7 +5747,7 @@
         <v>6.4</v>
       </c>
       <c r="DL12" t="n">
-        <v>0.5</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="DM12" t="n">
         <v>58.74</v>
@@ -5756,7 +5756,7 @@
         <v>0.64</v>
       </c>
       <c r="DO12" t="n">
-        <v>2.67</v>
+        <v>2.74</v>
       </c>
       <c r="DP12" t="n">
         <v>11.63</v>
@@ -5777,16 +5777,16 @@
         <v>0</v>
       </c>
       <c r="DV12" t="n">
-        <v>57.64</v>
+        <v>57.6</v>
       </c>
       <c r="DW12" t="n">
         <v>0.04</v>
       </c>
       <c r="DX12" t="n">
-        <v>15.8</v>
+        <v>15.77</v>
       </c>
       <c r="DY12" t="n">
-        <v>10.84</v>
+        <v>10.8</v>
       </c>
       <c r="DZ12" t="n">
         <v>4.96</v>
@@ -5795,7 +5795,7 @@
         <v>22.4</v>
       </c>
       <c r="EB12" t="n">
-        <v>1.77</v>
+        <v>1.76</v>
       </c>
       <c r="EC12" t="n">
         <v>1.7</v>
@@ -5961,10 +5961,10 @@
         <v>0.07000000000000001</v>
       </c>
       <c r="BA13" t="n">
-        <v>15.4</v>
+        <v>15.33</v>
       </c>
       <c r="BB13" t="n">
-        <v>9.73</v>
+        <v>9.67</v>
       </c>
       <c r="BC13" t="n">
         <v>5.67</v>
@@ -6186,10 +6186,10 @@
         <v>0.04</v>
       </c>
       <c r="DX13" t="n">
-        <v>14.46</v>
+        <v>14.43</v>
       </c>
       <c r="DY13" t="n">
-        <v>9.23</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="DZ13" t="n">
         <v>5.24</v>
@@ -6226,7 +6226,7 @@
         <v>1.53</v>
       </c>
       <c r="G14" t="n">
-        <v>3.13</v>
+        <v>3.4</v>
       </c>
       <c r="H14" t="n">
         <v>92.8</v>
@@ -6241,7 +6241,7 @@
         <v>6.67</v>
       </c>
       <c r="L14" t="n">
-        <v>1</v>
+        <v>1.07</v>
       </c>
       <c r="M14" t="n">
         <v>44.87</v>
@@ -6250,7 +6250,7 @@
         <v>1.27</v>
       </c>
       <c r="O14" t="n">
-        <v>3</v>
+        <v>3.27</v>
       </c>
       <c r="P14" t="n">
         <v>12.33</v>
@@ -6409,10 +6409,10 @@
         <v>1.27</v>
       </c>
       <c r="BP14" t="n">
-        <v>5.2</v>
+        <v>5.37</v>
       </c>
       <c r="BQ14" t="n">
-        <v>6.03</v>
+        <v>6.23</v>
       </c>
       <c r="BR14" t="n">
         <v>96.67</v>
@@ -6534,7 +6534,7 @@
         <v>1.33</v>
       </c>
       <c r="DG14" t="n">
-        <v>2.33</v>
+        <v>2.47</v>
       </c>
       <c r="DH14" t="n">
         <v>87.3</v>
@@ -6549,7 +6549,7 @@
         <v>4.77</v>
       </c>
       <c r="DL14" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.6</v>
       </c>
       <c r="DM14" t="n">
         <v>39.1</v>
@@ -6558,7 +6558,7 @@
         <v>0.97</v>
       </c>
       <c r="DO14" t="n">
-        <v>2.16</v>
+        <v>2.3</v>
       </c>
       <c r="DP14" t="n">
         <v>11.86</v>
@@ -6682,10 +6682,10 @@
         <v>0</v>
       </c>
       <c r="Z15" t="n">
-        <v>15.4</v>
+        <v>15.47</v>
       </c>
       <c r="AA15" t="n">
-        <v>10.27</v>
+        <v>10.33</v>
       </c>
       <c r="AB15" t="n">
         <v>5.13</v>
@@ -6694,7 +6694,7 @@
         <v>18</v>
       </c>
       <c r="AD15" t="n">
-        <v>1.73</v>
+        <v>1.74</v>
       </c>
       <c r="AE15" t="n">
         <v>1.33</v>
@@ -6988,10 +6988,10 @@
         <v>0</v>
       </c>
       <c r="DX15" t="n">
-        <v>14.86</v>
+        <v>14.9</v>
       </c>
       <c r="DY15" t="n">
-        <v>10.07</v>
+        <v>10.1</v>
       </c>
       <c r="DZ15" t="n">
         <v>4.8</v>
@@ -7000,7 +7000,7 @@
         <v>19.63</v>
       </c>
       <c r="EB15" t="n">
-        <v>1.63</v>
+        <v>1.64</v>
       </c>
       <c r="EC15" t="n">
         <v>1.4</v>
@@ -7436,7 +7436,7 @@
         <v>-0.07000000000000001</v>
       </c>
       <c r="J17" t="n">
-        <v>2.33</v>
+        <v>2.27</v>
       </c>
       <c r="K17" t="n">
         <v>5.47</v>
@@ -7448,7 +7448,7 @@
         <v>43.47</v>
       </c>
       <c r="N17" t="n">
-        <v>0.53</v>
+        <v>0.47</v>
       </c>
       <c r="O17" t="n">
         <v>2.07</v>
@@ -7478,16 +7478,16 @@
         <v>0</v>
       </c>
       <c r="X17" t="n">
-        <v>47.6</v>
+        <v>47.67</v>
       </c>
       <c r="Y17" t="n">
         <v>0.07000000000000001</v>
       </c>
       <c r="Z17" t="n">
-        <v>11</v>
+        <v>10.93</v>
       </c>
       <c r="AA17" t="n">
-        <v>7.47</v>
+        <v>7.4</v>
       </c>
       <c r="AB17" t="n">
         <v>3.53</v>
@@ -7499,7 +7499,7 @@
         <v>1.26</v>
       </c>
       <c r="AE17" t="n">
-        <v>2.27</v>
+        <v>2.2</v>
       </c>
       <c r="AF17" t="n">
         <v>0.13</v>
@@ -7744,7 +7744,7 @@
         <v>0</v>
       </c>
       <c r="DJ17" t="n">
-        <v>2.47</v>
+        <v>2.44</v>
       </c>
       <c r="DK17" t="n">
         <v>4.9</v>
@@ -7756,7 +7756,7 @@
         <v>40</v>
       </c>
       <c r="DN17" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.54</v>
       </c>
       <c r="DO17" t="n">
         <v>1.87</v>
@@ -7780,16 +7780,16 @@
         <v>0</v>
       </c>
       <c r="DV17" t="n">
-        <v>45.9</v>
+        <v>45.94</v>
       </c>
       <c r="DW17" t="n">
         <v>0.07000000000000001</v>
       </c>
       <c r="DX17" t="n">
-        <v>10.04</v>
+        <v>10</v>
       </c>
       <c r="DY17" t="n">
-        <v>6.9</v>
+        <v>6.86</v>
       </c>
       <c r="DZ17" t="n">
         <v>3.13</v>
@@ -7801,7 +7801,7 @@
         <v>1.14</v>
       </c>
       <c r="EC17" t="n">
-        <v>2.37</v>
+        <v>2.34</v>
       </c>
     </row>
   </sheetData>

--- a/data/teams/leagues/Averages_Sweden_Allsvenskan_2025.xlsx
+++ b/data/teams/leagues/Averages_Sweden_Allsvenskan_2025.xlsx
@@ -17,16 +17,13 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="1">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -37,7 +34,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -45,21 +42,12 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -706,667 +694,667 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>team_name</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>total_games</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>home_games</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>away_games</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>home_avg_0_10_min_goals</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>home_avg_2h_cards</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>home_avg_2h_corners</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>home_avg_attacks</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>home_avg_cards_0_10_min</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>home_avg_cards_num</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>home_avg_corners</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>home_avg_corners_0_10_min</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="M1" t="inlineStr">
         <is>
           <t>home_avg_dangerous_attacks</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="N1" t="inlineStr">
         <is>
           <t>home_avg_fh_cards</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="O1" t="inlineStr">
         <is>
           <t>home_avg_fh_corners</t>
         </is>
       </c>
-      <c r="P1" s="1" t="inlineStr">
+      <c r="P1" t="inlineStr">
         <is>
           <t>home_avg_fouls</t>
         </is>
       </c>
-      <c r="Q1" s="1" t="inlineStr">
+      <c r="Q1" t="inlineStr">
         <is>
           <t>home_avg_freekicks</t>
         </is>
       </c>
-      <c r="R1" s="1" t="inlineStr">
+      <c r="R1" t="inlineStr">
         <is>
           <t>home_avg_goalkicks</t>
         </is>
       </c>
-      <c r="S1" s="1" t="inlineStr">
+      <c r="S1" t="inlineStr">
         <is>
           <t>home_avg_goals_conceded</t>
         </is>
       </c>
-      <c r="T1" s="1" t="inlineStr">
+      <c r="T1" t="inlineStr">
         <is>
           <t>home_avg_goals_scored</t>
         </is>
       </c>
-      <c r="U1" s="1" t="inlineStr">
+      <c r="U1" t="inlineStr">
         <is>
           <t>home_avg_penalties_won</t>
         </is>
       </c>
-      <c r="V1" s="1" t="inlineStr">
+      <c r="V1" t="inlineStr">
         <is>
           <t>home_avg_penalty_goals</t>
         </is>
       </c>
-      <c r="W1" s="1" t="inlineStr">
+      <c r="W1" t="inlineStr">
         <is>
           <t>home_avg_penalty_missed</t>
         </is>
       </c>
-      <c r="X1" s="1" t="inlineStr">
+      <c r="X1" t="inlineStr">
         <is>
           <t>home_avg_possession</t>
         </is>
       </c>
-      <c r="Y1" s="1" t="inlineStr">
+      <c r="Y1" t="inlineStr">
         <is>
           <t>home_avg_red_cards</t>
         </is>
       </c>
-      <c r="Z1" s="1" t="inlineStr">
+      <c r="Z1" t="inlineStr">
         <is>
           <t>home_avg_shots</t>
         </is>
       </c>
-      <c r="AA1" s="1" t="inlineStr">
+      <c r="AA1" t="inlineStr">
         <is>
           <t>home_avg_shotsOffTarget</t>
         </is>
       </c>
-      <c r="AB1" s="1" t="inlineStr">
+      <c r="AB1" t="inlineStr">
         <is>
           <t>home_avg_shotsOnTarget</t>
         </is>
       </c>
-      <c r="AC1" s="1" t="inlineStr">
+      <c r="AC1" t="inlineStr">
         <is>
           <t>home_avg_throwins</t>
         </is>
       </c>
-      <c r="AD1" s="1" t="inlineStr">
+      <c r="AD1" t="inlineStr">
         <is>
           <t>home_avg_xg</t>
         </is>
       </c>
-      <c r="AE1" s="1" t="inlineStr">
+      <c r="AE1" t="inlineStr">
         <is>
           <t>home_avg_yellow_cards</t>
         </is>
       </c>
-      <c r="AF1" s="1" t="inlineStr">
+      <c r="AF1" t="inlineStr">
         <is>
           <t>away_avg_0_10_min_goals</t>
         </is>
       </c>
-      <c r="AG1" s="1" t="inlineStr">
+      <c r="AG1" t="inlineStr">
         <is>
           <t>away_avg_2h_cards</t>
         </is>
       </c>
-      <c r="AH1" s="1" t="inlineStr">
+      <c r="AH1" t="inlineStr">
         <is>
           <t>away_avg_2h_corners</t>
         </is>
       </c>
-      <c r="AI1" s="1" t="inlineStr">
+      <c r="AI1" t="inlineStr">
         <is>
           <t>away_avg_attacks</t>
         </is>
       </c>
-      <c r="AJ1" s="1" t="inlineStr">
+      <c r="AJ1" t="inlineStr">
         <is>
           <t>away_avg_cards_0_10_min</t>
         </is>
       </c>
-      <c r="AK1" s="1" t="inlineStr">
+      <c r="AK1" t="inlineStr">
         <is>
           <t>away_avg_cards_num</t>
         </is>
       </c>
-      <c r="AL1" s="1" t="inlineStr">
+      <c r="AL1" t="inlineStr">
         <is>
           <t>away_avg_corners</t>
         </is>
       </c>
-      <c r="AM1" s="1" t="inlineStr">
+      <c r="AM1" t="inlineStr">
         <is>
           <t>away_avg_corners_0_10_min</t>
         </is>
       </c>
-      <c r="AN1" s="1" t="inlineStr">
+      <c r="AN1" t="inlineStr">
         <is>
           <t>away_avg_dangerous_attacks</t>
         </is>
       </c>
-      <c r="AO1" s="1" t="inlineStr">
+      <c r="AO1" t="inlineStr">
         <is>
           <t>away_avg_fh_cards</t>
         </is>
       </c>
-      <c r="AP1" s="1" t="inlineStr">
+      <c r="AP1" t="inlineStr">
         <is>
           <t>away_avg_fh_corners</t>
         </is>
       </c>
-      <c r="AQ1" s="1" t="inlineStr">
+      <c r="AQ1" t="inlineStr">
         <is>
           <t>away_avg_fouls</t>
         </is>
       </c>
-      <c r="AR1" s="1" t="inlineStr">
+      <c r="AR1" t="inlineStr">
         <is>
           <t>away_avg_freekicks</t>
         </is>
       </c>
-      <c r="AS1" s="1" t="inlineStr">
+      <c r="AS1" t="inlineStr">
         <is>
           <t>away_avg_goalkicks</t>
         </is>
       </c>
-      <c r="AT1" s="1" t="inlineStr">
+      <c r="AT1" t="inlineStr">
         <is>
           <t>away_avg_goals_conceded</t>
         </is>
       </c>
-      <c r="AU1" s="1" t="inlineStr">
+      <c r="AU1" t="inlineStr">
         <is>
           <t>away_avg_goals_scored</t>
         </is>
       </c>
-      <c r="AV1" s="1" t="inlineStr">
+      <c r="AV1" t="inlineStr">
         <is>
           <t>away_avg_penalties_won</t>
         </is>
       </c>
-      <c r="AW1" s="1" t="inlineStr">
+      <c r="AW1" t="inlineStr">
         <is>
           <t>away_avg_penalty_goals</t>
         </is>
       </c>
-      <c r="AX1" s="1" t="inlineStr">
+      <c r="AX1" t="inlineStr">
         <is>
           <t>away_avg_penalty_missed</t>
         </is>
       </c>
-      <c r="AY1" s="1" t="inlineStr">
+      <c r="AY1" t="inlineStr">
         <is>
           <t>away_avg_possession</t>
         </is>
       </c>
-      <c r="AZ1" s="1" t="inlineStr">
+      <c r="AZ1" t="inlineStr">
         <is>
           <t>away_avg_red_cards</t>
         </is>
       </c>
-      <c r="BA1" s="1" t="inlineStr">
+      <c r="BA1" t="inlineStr">
         <is>
           <t>away_avg_shots</t>
         </is>
       </c>
-      <c r="BB1" s="1" t="inlineStr">
+      <c r="BB1" t="inlineStr">
         <is>
           <t>away_avg_shotsOffTarget</t>
         </is>
       </c>
-      <c r="BC1" s="1" t="inlineStr">
+      <c r="BC1" t="inlineStr">
         <is>
           <t>away_avg_shotsOnTarget</t>
         </is>
       </c>
-      <c r="BD1" s="1" t="inlineStr">
+      <c r="BD1" t="inlineStr">
         <is>
           <t>away_avg_throwins</t>
         </is>
       </c>
-      <c r="BE1" s="1" t="inlineStr">
+      <c r="BE1" t="inlineStr">
         <is>
           <t>away_avg_xg</t>
         </is>
       </c>
-      <c r="BF1" s="1" t="inlineStr">
+      <c r="BF1" t="inlineStr">
         <is>
           <t>away_avg_yellow_cards</t>
         </is>
       </c>
-      <c r="BG1" s="1" t="inlineStr">
+      <c r="BG1" t="inlineStr">
         <is>
           <t>totalGoalCount</t>
         </is>
       </c>
-      <c r="BH1" s="1" t="inlineStr">
+      <c r="BH1" t="inlineStr">
         <is>
           <t>totalCornerCount</t>
         </is>
       </c>
-      <c r="BI1" s="1" t="inlineStr">
+      <c r="BI1" t="inlineStr">
         <is>
           <t>overallGoalCount</t>
         </is>
       </c>
-      <c r="BJ1" s="1" t="inlineStr">
+      <c r="BJ1" t="inlineStr">
         <is>
           <t>ht_goals_team_a</t>
         </is>
       </c>
-      <c r="BK1" s="1" t="inlineStr">
+      <c r="BK1" t="inlineStr">
         <is>
           <t>ht_goals_team_b</t>
         </is>
       </c>
-      <c r="BL1" s="1" t="inlineStr">
+      <c r="BL1" t="inlineStr">
         <is>
           <t>goals_2hg_team_a</t>
         </is>
       </c>
-      <c r="BM1" s="1" t="inlineStr">
+      <c r="BM1" t="inlineStr">
         <is>
           <t>goals_2hg_team_b</t>
         </is>
       </c>
-      <c r="BN1" s="1" t="inlineStr">
+      <c r="BN1" t="inlineStr">
         <is>
           <t>GoalCount_2hg</t>
         </is>
       </c>
-      <c r="BO1" s="1" t="inlineStr">
+      <c r="BO1" t="inlineStr">
         <is>
           <t>HTGoalCount</t>
         </is>
       </c>
-      <c r="BP1" s="1" t="inlineStr">
+      <c r="BP1" t="inlineStr">
         <is>
           <t>corner_fh_count</t>
         </is>
       </c>
-      <c r="BQ1" s="1" t="inlineStr">
+      <c r="BQ1" t="inlineStr">
         <is>
           <t>corner_2h_count</t>
         </is>
       </c>
-      <c r="BR1" s="1" t="inlineStr">
+      <c r="BR1" t="inlineStr">
         <is>
           <t>over05</t>
         </is>
       </c>
-      <c r="BS1" s="1" t="inlineStr">
+      <c r="BS1" t="inlineStr">
         <is>
           <t>over15</t>
         </is>
       </c>
-      <c r="BT1" s="1" t="inlineStr">
+      <c r="BT1" t="inlineStr">
         <is>
           <t>over25</t>
         </is>
       </c>
-      <c r="BU1" s="1" t="inlineStr">
+      <c r="BU1" t="inlineStr">
         <is>
           <t>over35</t>
         </is>
       </c>
-      <c r="BV1" s="1" t="inlineStr">
+      <c r="BV1" t="inlineStr">
         <is>
           <t>over45</t>
         </is>
       </c>
-      <c r="BW1" s="1" t="inlineStr">
+      <c r="BW1" t="inlineStr">
         <is>
           <t>over55</t>
         </is>
       </c>
-      <c r="BX1" s="1" t="inlineStr">
+      <c r="BX1" t="inlineStr">
         <is>
           <t>btts</t>
         </is>
       </c>
-      <c r="BY1" s="1" t="inlineStr">
+      <c r="BY1" t="inlineStr">
         <is>
           <t>avg_odds_ft_1</t>
         </is>
       </c>
-      <c r="BZ1" s="1" t="inlineStr">
+      <c r="BZ1" t="inlineStr">
         <is>
           <t>avg_pinnacle_ft_1_odd</t>
         </is>
       </c>
-      <c r="CA1" s="1" t="inlineStr">
+      <c r="CA1" t="inlineStr">
         <is>
           <t>avg_odds_ft_x</t>
         </is>
       </c>
-      <c r="CB1" s="1" t="inlineStr">
+      <c r="CB1" t="inlineStr">
         <is>
           <t>avg_pinnacle_ft_x_odd</t>
         </is>
       </c>
-      <c r="CC1" s="1" t="inlineStr">
+      <c r="CC1" t="inlineStr">
         <is>
           <t>avg_odds_ft_2</t>
         </is>
       </c>
-      <c r="CD1" s="1" t="inlineStr">
+      <c r="CD1" t="inlineStr">
         <is>
           <t>avg_pinnacle_ft_2_odd</t>
         </is>
       </c>
-      <c r="CE1" s="1" t="inlineStr">
+      <c r="CE1" t="inlineStr">
         <is>
           <t>avg_odds_1st_half_over05</t>
         </is>
       </c>
-      <c r="CF1" s="1" t="inlineStr">
+      <c r="CF1" t="inlineStr">
         <is>
           <t>avg_odds_1st_half_over15</t>
         </is>
       </c>
-      <c r="CG1" s="1" t="inlineStr">
+      <c r="CG1" t="inlineStr">
         <is>
           <t>avg_odds_1st_half_under05</t>
         </is>
       </c>
-      <c r="CH1" s="1" t="inlineStr">
+      <c r="CH1" t="inlineStr">
         <is>
           <t>avg_odds_1st_half_under15</t>
         </is>
       </c>
-      <c r="CI1" s="1" t="inlineStr">
+      <c r="CI1" t="inlineStr">
         <is>
           <t>avg_odds_btts_no</t>
         </is>
       </c>
-      <c r="CJ1" s="1" t="inlineStr">
+      <c r="CJ1" t="inlineStr">
         <is>
           <t>avg_odds_btts_yes</t>
         </is>
       </c>
-      <c r="CK1" s="1" t="inlineStr">
+      <c r="CK1" t="inlineStr">
         <is>
           <t>avg_odds_corners_over_85</t>
         </is>
       </c>
-      <c r="CL1" s="1" t="inlineStr">
+      <c r="CL1" t="inlineStr">
         <is>
           <t>avg_odds_corners_over_95</t>
         </is>
       </c>
-      <c r="CM1" s="1" t="inlineStr">
+      <c r="CM1" t="inlineStr">
         <is>
           <t>avg_odds_corners_under_85</t>
         </is>
       </c>
-      <c r="CN1" s="1" t="inlineStr">
+      <c r="CN1" t="inlineStr">
         <is>
           <t>avg_odds_corners_under_95</t>
         </is>
       </c>
-      <c r="CO1" s="1" t="inlineStr">
+      <c r="CO1" t="inlineStr">
         <is>
           <t>avg_odds_ft_over15</t>
         </is>
       </c>
-      <c r="CP1" s="1" t="inlineStr">
+      <c r="CP1" t="inlineStr">
         <is>
           <t>avg_odds_ft_over25</t>
         </is>
       </c>
-      <c r="CQ1" s="1" t="inlineStr">
+      <c r="CQ1" t="inlineStr">
         <is>
           <t>avg_odds_ft_over35</t>
         </is>
       </c>
-      <c r="CR1" s="1" t="inlineStr">
+      <c r="CR1" t="inlineStr">
         <is>
           <t>avg_pinnacle_1st_half_over05_odd</t>
         </is>
       </c>
-      <c r="CS1" s="1" t="inlineStr">
+      <c r="CS1" t="inlineStr">
         <is>
           <t>avg_pinnacle_1st_half_over15_odd</t>
         </is>
       </c>
-      <c r="CT1" s="1" t="inlineStr">
+      <c r="CT1" t="inlineStr">
         <is>
           <t>avg_pinnacle_1st_half_under05_odd</t>
         </is>
       </c>
-      <c r="CU1" s="1" t="inlineStr">
+      <c r="CU1" t="inlineStr">
         <is>
           <t>avg_pinnacle_1st_half_under15_odd</t>
         </is>
       </c>
-      <c r="CV1" s="1" t="inlineStr">
+      <c r="CV1" t="inlineStr">
         <is>
           <t>avg_pinnacle_btts_no_odd</t>
         </is>
       </c>
-      <c r="CW1" s="1" t="inlineStr">
+      <c r="CW1" t="inlineStr">
         <is>
           <t>avg_pinnacle_btts_yes_odd</t>
         </is>
       </c>
-      <c r="CX1" s="1" t="inlineStr">
+      <c r="CX1" t="inlineStr">
         <is>
           <t>avg_pinnacle_corners_over_85_odd</t>
         </is>
       </c>
-      <c r="CY1" s="1" t="inlineStr">
+      <c r="CY1" t="inlineStr">
         <is>
           <t>avg_pinnacle_corners_over_95_odd</t>
         </is>
       </c>
-      <c r="CZ1" s="1" t="inlineStr">
+      <c r="CZ1" t="inlineStr">
         <is>
           <t>avg_pinnacle_corners_under_85_odd</t>
         </is>
       </c>
-      <c r="DA1" s="1" t="inlineStr">
+      <c r="DA1" t="inlineStr">
         <is>
           <t>avg_pinnacle_corners_under_95_odd</t>
         </is>
       </c>
-      <c r="DB1" s="1" t="inlineStr">
+      <c r="DB1" t="inlineStr">
         <is>
           <t>avg_pinnacle_ft_over15_odd</t>
         </is>
       </c>
-      <c r="DC1" s="1" t="inlineStr">
+      <c r="DC1" t="inlineStr">
         <is>
           <t>avg_pinnacle_ft_over25_odd</t>
         </is>
       </c>
-      <c r="DD1" s="1" t="inlineStr">
+      <c r="DD1" t="inlineStr">
         <is>
           <t>avg_pinnacle_ft_over35_odd</t>
         </is>
       </c>
-      <c r="DE1" s="1" t="inlineStr">
+      <c r="DE1" t="inlineStr">
         <is>
           <t>total_avg_0_10_min_goals</t>
         </is>
       </c>
-      <c r="DF1" s="1" t="inlineStr">
+      <c r="DF1" t="inlineStr">
         <is>
           <t>total_avg_2h_cards</t>
         </is>
       </c>
-      <c r="DG1" s="1" t="inlineStr">
+      <c r="DG1" t="inlineStr">
         <is>
           <t>total_avg_2h_corners</t>
         </is>
       </c>
-      <c r="DH1" s="1" t="inlineStr">
+      <c r="DH1" t="inlineStr">
         <is>
           <t>total_avg_attacks</t>
         </is>
       </c>
-      <c r="DI1" s="1" t="inlineStr">
+      <c r="DI1" t="inlineStr">
         <is>
           <t>total_avg_cards_0_10_min</t>
         </is>
       </c>
-      <c r="DJ1" s="1" t="inlineStr">
+      <c r="DJ1" t="inlineStr">
         <is>
           <t>total_avg_cards_num</t>
         </is>
       </c>
-      <c r="DK1" s="1" t="inlineStr">
+      <c r="DK1" t="inlineStr">
         <is>
           <t>total_avg_corners</t>
         </is>
       </c>
-      <c r="DL1" s="1" t="inlineStr">
+      <c r="DL1" t="inlineStr">
         <is>
           <t>total_avg_corners_0_10_min</t>
         </is>
       </c>
-      <c r="DM1" s="1" t="inlineStr">
+      <c r="DM1" t="inlineStr">
         <is>
           <t>total_avg_dangerous_attacks</t>
         </is>
       </c>
-      <c r="DN1" s="1" t="inlineStr">
+      <c r="DN1" t="inlineStr">
         <is>
           <t>total_avg_fh_cards</t>
         </is>
       </c>
-      <c r="DO1" s="1" t="inlineStr">
+      <c r="DO1" t="inlineStr">
         <is>
           <t>total_avg_fh_corners</t>
         </is>
       </c>
-      <c r="DP1" s="1" t="inlineStr">
+      <c r="DP1" t="inlineStr">
         <is>
           <t>total_avg_fouls</t>
         </is>
       </c>
-      <c r="DQ1" s="1" t="inlineStr">
+      <c r="DQ1" t="inlineStr">
         <is>
           <t>total_avg_freekicks</t>
         </is>
       </c>
-      <c r="DR1" s="1" t="inlineStr">
+      <c r="DR1" t="inlineStr">
         <is>
           <t>total_avg_goalkicks</t>
         </is>
       </c>
-      <c r="DS1" s="1" t="inlineStr">
+      <c r="DS1" t="inlineStr">
         <is>
           <t>total_avg_penalties_won</t>
         </is>
       </c>
-      <c r="DT1" s="1" t="inlineStr">
+      <c r="DT1" t="inlineStr">
         <is>
           <t>total_avg_penalty_goals</t>
         </is>
       </c>
-      <c r="DU1" s="1" t="inlineStr">
+      <c r="DU1" t="inlineStr">
         <is>
           <t>total_avg_penalty_missed</t>
         </is>
       </c>
-      <c r="DV1" s="1" t="inlineStr">
+      <c r="DV1" t="inlineStr">
         <is>
           <t>total_avg_possession</t>
         </is>
       </c>
-      <c r="DW1" s="1" t="inlineStr">
+      <c r="DW1" t="inlineStr">
         <is>
           <t>total_avg_red_cards</t>
         </is>
       </c>
-      <c r="DX1" s="1" t="inlineStr">
+      <c r="DX1" t="inlineStr">
         <is>
           <t>total_avg_shots</t>
         </is>
       </c>
-      <c r="DY1" s="1" t="inlineStr">
+      <c r="DY1" t="inlineStr">
         <is>
           <t>total_avg_shotsOffTarget</t>
         </is>
       </c>
-      <c r="DZ1" s="1" t="inlineStr">
+      <c r="DZ1" t="inlineStr">
         <is>
           <t>total_avg_shotsOnTarget</t>
         </is>
       </c>
-      <c r="EA1" s="1" t="inlineStr">
+      <c r="EA1" t="inlineStr">
         <is>
           <t>total_avg_throwins</t>
         </is>
       </c>
-      <c r="EB1" s="1" t="inlineStr">
+      <c r="EB1" t="inlineStr">
         <is>
           <t>total_avg_xg</t>
         </is>
       </c>
-      <c r="EC1" s="1" t="inlineStr">
+      <c r="EC1" t="inlineStr">
         <is>
           <t>total_avg_yellow_cards</t>
         </is>
